--- a/artfynd/A 57297-2020 artfynd.xlsx
+++ b/artfynd/A 57297-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123450961</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>123450972</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57297-2020 artfynd.xlsx
+++ b/artfynd/A 57297-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123450972</v>
+        <v>123450961</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474298</v>
+        <v>474311</v>
       </c>
       <c r="R2" t="n">
-        <v>6594832</v>
+        <v>6594789</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123450961</v>
+        <v>123450972</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474311</v>
+        <v>474298</v>
       </c>
       <c r="R3" t="n">
-        <v>6594789</v>
+        <v>6594832</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 57297-2020 artfynd.xlsx
+++ b/artfynd/A 57297-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123450961</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>123450972</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57297-2020 artfynd.xlsx
+++ b/artfynd/A 57297-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123450961</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>123450972</v>
       </c>
       <c r="B3" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
